--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487154_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487154_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.0416</v>
+        <v>3.2861</v>
       </c>
       <c r="E2" t="n">
-        <v>3.8313</v>
+        <v>3.5308</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2103</v>
+        <v>-0.2448</v>
       </c>
       <c r="G2" t="n">
         <v>1.5194</v>
@@ -610,13 +610,13 @@
         <v>0.772</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0939</v>
+        <v>0.3384</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4442</v>
+        <v>0.1438</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6497000000000001</v>
+        <v>0.1946</v>
       </c>
       <c r="V2" t="n">
         <v>0.6562</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. LOPEZ BRETON</t>
+          <t>G. HUESO GUTIERREZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3046</v>
+        <v>1.7087</v>
       </c>
       <c r="E3" t="n">
-        <v>3.9585</v>
+        <v>6.8406</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.6539</v>
+        <v>-5.1319</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.2729</v>
+        <v>4.6808</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.1201</v>
+        <v>3.8582</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1528</v>
+        <v>0.8225</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9277</v>
+        <v>8.429500000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1137</v>
+        <v>3.9119</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8139999999999999</v>
+        <v>4.5176</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.2006</v>
+        <v>-3.7488</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2338</v>
+        <v>-0.0537</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.9668</v>
+        <v>-3.6951</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.579</v>
+        <v>0.193</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.9301</v>
+        <v>-0.965</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3511</v>
+        <v>1.158</v>
       </c>
       <c r="S3" t="n">
-        <v>1.7272</v>
+        <v>-0.8722</v>
       </c>
       <c r="T3" t="n">
-        <v>1.6895</v>
+        <v>-0.2958</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0377</v>
+        <v>-0.5764</v>
       </c>
       <c r="V3" t="n">
-        <v>1.4293</v>
+        <v>-2.2929</v>
       </c>
       <c r="W3" t="n">
-        <v>3.2713</v>
+        <v>-0.3281</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.842</v>
+        <v>-1.9647</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. MARTINEZ DE OSABA ANTOLIN</t>
+          <t>A. LOPEZ BRETON</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1239</v>
+        <v>1.323</v>
       </c>
       <c r="E4" t="n">
-        <v>3.9347</v>
+        <v>3.0572</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.8109</v>
+        <v>-1.7342</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.3419</v>
+        <v>-0.2729</v>
       </c>
       <c r="H4" t="n">
-        <v>3.9008</v>
+        <v>-0.1201</v>
       </c>
       <c r="I4" t="n">
-        <v>-4.2427</v>
+        <v>-0.1528</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1199</v>
+        <v>0.9277</v>
       </c>
       <c r="K4" t="n">
-        <v>3.674</v>
+        <v>0.1137</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.5541</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.4619</v>
+        <v>-1.2006</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2268</v>
+        <v>-0.2338</v>
       </c>
       <c r="O4" t="n">
-        <v>-3.6886</v>
+        <v>-0.9668</v>
       </c>
       <c r="P4" t="n">
-        <v>0.386</v>
+        <v>-0.579</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="R4" t="n">
         <v>1.3511</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8745000000000001</v>
+        <v>0.7456</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0621</v>
+        <v>0.7883</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9366</v>
+        <v>-0.0427</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2053</v>
+        <v>1.4293</v>
       </c>
       <c r="W4" t="n">
-        <v>1.842</v>
+        <v>3.2713</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.6366</v>
+        <v>-1.842</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. HUESO GUTIERREZ</t>
+          <t>G. MARTINEZ DE OSABA ANTOLIN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4129</v>
+        <v>0.5211</v>
       </c>
       <c r="E5" t="n">
-        <v>6.0801</v>
+        <v>3.8941</v>
       </c>
       <c r="F5" t="n">
-        <v>-5.6673</v>
+        <v>-3.373</v>
       </c>
       <c r="G5" t="n">
-        <v>4.6808</v>
+        <v>-0.3419</v>
       </c>
       <c r="H5" t="n">
-        <v>3.8582</v>
+        <v>3.9008</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8225</v>
+        <v>-4.2427</v>
       </c>
       <c r="J5" t="n">
-        <v>8.429500000000001</v>
+        <v>3.1199</v>
       </c>
       <c r="K5" t="n">
-        <v>3.9119</v>
+        <v>3.674</v>
       </c>
       <c r="L5" t="n">
-        <v>4.5176</v>
+        <v>-0.5541</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.7488</v>
+        <v>-3.4619</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0537</v>
+        <v>0.2268</v>
       </c>
       <c r="O5" t="n">
-        <v>-3.6951</v>
+        <v>-3.6886</v>
       </c>
       <c r="P5" t="n">
-        <v>0.193</v>
+        <v>0.386</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.965</v>
       </c>
       <c r="R5" t="n">
-        <v>1.158</v>
+        <v>1.3511</v>
       </c>
       <c r="S5" t="n">
-        <v>-2.168</v>
+        <v>0.2717</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0562</v>
+        <v>-0.1028</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.1118</v>
+        <v>0.3744</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.2929</v>
+        <v>0.2053</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.3281</v>
+        <v>1.842</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.9647</v>
+        <v>-1.6366</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.4794</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3826</v>
+        <v>0.0775</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4554</v>
+        <v>0.4019</v>
       </c>
       <c r="G6" t="n">
         <v>1.1027</v>
@@ -922,13 +922,13 @@
         <v>1.3511</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4508</v>
+        <v>-0.0443</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2089</v>
+        <v>0.2512</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2419</v>
+        <v>-0.2955</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1928</v>
+        <v>0.2137</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1585</v>
+        <v>1.6185</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.3513</v>
+        <v>-1.4048</v>
       </c>
       <c r="G7" t="n">
         <v>1.7464</v>
@@ -1000,13 +1000,13 @@
         <v>1.3511</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.2374</v>
+        <v>-0.8309</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8923</v>
+        <v>-0.4323</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3451</v>
+        <v>-0.3986</v>
       </c>
       <c r="V7" t="n">
         <v>-0.1228</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L. DIEZ TIDALA</t>
+          <t>P. MOLINA MATA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0359</v>
+        <v>-0.9733000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2356</v>
+        <v>1.3264</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2715</v>
+        <v>-2.2998</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1113</v>
+        <v>-0.3434</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1863</v>
+        <v>0.8405</v>
       </c>
       <c r="I8" t="n">
-        <v>0.075</v>
+        <v>-1.1838</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1021</v>
+        <v>1.2101</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0207</v>
+        <v>0.6002999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0814</v>
+        <v>0.6098</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2134</v>
+        <v>-1.5534</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.207</v>
+        <v>0.2402</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0064</v>
+        <v>-1.7936</v>
       </c>
       <c r="P8" t="n">
-        <v>0.193</v>
+        <v>1.9301</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.193</v>
+        <v>1.9301</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1104</v>
+        <v>-0.1041</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1335</v>
+        <v>0.1164</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0231</v>
+        <v>-0.2205</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.228</v>
+        <v>-2.4559</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.228</v>
+        <v>-2.4559</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. MOLINA MATA</t>
+          <t>L. DIEZ TIDALA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6009</v>
+        <v>-1.1162</v>
       </c>
       <c r="E9" t="n">
-        <v>1.2075</v>
+        <v>0.2356</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.8084</v>
+        <v>-1.3518</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3434</v>
+        <v>-0.1113</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8405</v>
+        <v>-0.1863</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.1838</v>
+        <v>0.075</v>
       </c>
       <c r="J9" t="n">
-        <v>1.2101</v>
+        <v>0.1021</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6002999999999999</v>
+        <v>0.0207</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6098</v>
+        <v>0.0814</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.5534</v>
+        <v>-0.2134</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2402</v>
+        <v>-0.207</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.7936</v>
+        <v>-0.0064</v>
       </c>
       <c r="P9" t="n">
-        <v>1.9301</v>
+        <v>0.193</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.9301</v>
+        <v>0.193</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7317</v>
+        <v>0.0301</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0026</v>
+        <v>0.1335</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7291</v>
+        <v>-0.1035</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.4559</v>
+        <v>-1.228</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.4559</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.7992</v>
+        <v>-1.5999</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0078</v>
+        <v>-0.8889</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7914</v>
+        <v>-0.7111</v>
       </c>
       <c r="G10" t="n">
         <v>-0.6241</v>
@@ -1234,13 +1234,13 @@
         <v>0.386</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8666</v>
+        <v>-0.6673</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4164</v>
+        <v>-0.2974</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4501</v>
+        <v>-0.3698</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6945</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>U. CALVO ARRUZA</t>
+          <t>A. JUSTO ANTOLIN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.9753</v>
+        <v>-1.8232</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.0019</v>
+        <v>0.2391</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9733000000000001</v>
+        <v>-2.0623</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.8788</v>
+        <v>-1.7049</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.2391</v>
+        <v>0.5971</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6398</v>
+        <v>-2.302</v>
       </c>
       <c r="J11" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.1821</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0414</v>
+        <v>0.1499</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0407</v>
+        <v>0.0321</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.9609</v>
+        <v>-1.887</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2805</v>
+        <v>0.4472</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6805</v>
+        <v>-2.3341</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.965</v>
+        <v>0.193</v>
       </c>
       <c r="Q11" t="n">
         <v>-0.965</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.158</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0086</v>
+        <v>-0.0255</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.119</v>
+        <v>-0.2059</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1104</v>
+        <v>0.1804</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.1228</v>
+        <v>-0.2859</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.228</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.1228</v>
+        <v>-1.5138</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. JUSTO ANTOLIN</t>
+          <t>U. CALVO ARRUZA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.1772</v>
+        <v>-1.9961</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.0613</v>
+        <v>-0.9424</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.1159</v>
+        <v>-1.0537</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.7049</v>
+        <v>-0.8788</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5971</v>
+        <v>-0.2391</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.302</v>
+        <v>-0.6398</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1821</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1499</v>
+        <v>0.0414</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0321</v>
+        <v>0.0407</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.887</v>
+        <v>-0.9609</v>
       </c>
       <c r="N12" t="n">
-        <v>0.4472</v>
+        <v>-0.2805</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.3341</v>
+        <v>-0.6805</v>
       </c>
       <c r="P12" t="n">
-        <v>0.193</v>
+        <v>-0.965</v>
       </c>
       <c r="Q12" t="n">
         <v>-0.965</v>
       </c>
       <c r="R12" t="n">
-        <v>1.158</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3794</v>
+        <v>-0.0294</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5063</v>
+        <v>-0.0595</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1269</v>
+        <v>0.0301</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.2859</v>
+        <v>-0.1228</v>
       </c>
       <c r="W12" t="n">
-        <v>1.228</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.5138</v>
+        <v>-0.1228</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.8301</v>
+        <v>-3.0839</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.7635</v>
+        <v>-3.2048</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.06660000000000001</v>
+        <v>0.1208</v>
       </c>
       <c r="G13" t="n">
         <v>-1.5243</v>
@@ -1468,13 +1468,13 @@
         <v>1.5441</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3312</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>0.977</v>
+        <v>0.5358000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6458</v>
+        <v>-0.4584</v>
       </c>
       <c r="V13" t="n">
         <v>-0.2859</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.655500000000001</v>
+        <v>-3.0606</v>
       </c>
       <c r="E14" t="n">
-        <v>15.1891</v>
+        <v>15.7837</v>
       </c>
       <c r="F14" t="n">
-        <v>-18.8448</v>
+        <v>-18.8447</v>
       </c>
       <c r="G14" t="n">
         <v>3.247699999999999</v>
@@ -1537,7 +1537,7 @@
         <v>-19.2073</v>
       </c>
       <c r="P14" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>6.661338147750939e-16</v>
       </c>
       <c r="Q14" t="n">
         <v>-12.5454</v>
@@ -1546,19 +1546,19 @@
         <v>12.5456</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.7053</v>
+        <v>-1.1106</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.01959999999999984</v>
+        <v>0.5753</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.6856</v>
+        <v>-1.6859</v>
       </c>
       <c r="V14" t="n">
-        <v>-5.1979</v>
+        <v>-5.197899999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>6.299099999999999</v>
+        <v>6.2991</v>
       </c>
       <c r="X14" t="n">
         <v>-11.4966</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S. CAMPBELL</t>
+          <t>R. CARTÓN CHARFOLE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.7479</v>
+        <v>5.0286</v>
       </c>
       <c r="E15" t="n">
-        <v>7.9912</v>
+        <v>5.5033</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.2432</v>
+        <v>-0.4747</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.2079</v>
+        <v>3.099</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.6874</v>
+        <v>-1.6921</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5205</v>
+        <v>4.7911</v>
       </c>
       <c r="J15" t="n">
-        <v>2.3088</v>
+        <v>5.2273</v>
       </c>
       <c r="K15" t="n">
-        <v>1.1692</v>
+        <v>-0.5434</v>
       </c>
       <c r="L15" t="n">
-        <v>1.1396</v>
+        <v>5.7707</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.5167</v>
+        <v>-2.1283</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.8566</v>
+        <v>-1.1487</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.6601</v>
+        <v>-0.9797</v>
       </c>
       <c r="P15" t="n">
-        <v>1.3511</v>
+        <v>0.965</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3161</v>
+        <v>0.965</v>
       </c>
       <c r="S15" t="n">
-        <v>5.2767</v>
+        <v>0.3083</v>
       </c>
       <c r="T15" t="n">
-        <v>4.8478</v>
+        <v>0.276</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4289</v>
+        <v>0.0324</v>
       </c>
       <c r="V15" t="n">
-        <v>0.3281</v>
+        <v>0.6562</v>
       </c>
       <c r="W15" t="n">
-        <v>1.7997</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.4716</v>
+        <v>0.6562</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. CARTÓN CHARFOLE</t>
+          <t>D. MERKVILADZE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.982</v>
+        <v>2.6563</v>
       </c>
       <c r="E16" t="n">
-        <v>5.8037</v>
+        <v>5.6376</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8217</v>
+        <v>-2.9813</v>
       </c>
       <c r="G16" t="n">
-        <v>3.099</v>
+        <v>3.121</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.6921</v>
+        <v>-0.8983</v>
       </c>
       <c r="I16" t="n">
-        <v>4.7911</v>
+        <v>4.0192</v>
       </c>
       <c r="J16" t="n">
-        <v>5.2273</v>
+        <v>6.9111</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.5434</v>
+        <v>1.0918</v>
       </c>
       <c r="L16" t="n">
-        <v>5.7707</v>
+        <v>5.8193</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.1283</v>
+        <v>-3.7902</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.1487</v>
+        <v>-1.9901</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.9797</v>
+        <v>-1.8001</v>
       </c>
       <c r="P16" t="n">
-        <v>0.965</v>
+        <v>-0.965</v>
       </c>
       <c r="Q16" t="n">
+        <v>-2.8951</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.9301</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.5004</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.3937</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.1067</v>
+      </c>
+      <c r="V16" t="n">
         <v>0</v>
       </c>
-      <c r="R16" t="n">
-        <v>0.965</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0.2617</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0.5764</v>
-      </c>
-      <c r="U16" t="n">
-        <v>-0.3147</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0.6562</v>
-      </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.228</v>
       </c>
       <c r="X16" t="n">
-        <v>0.6562</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. MERKVILADZE</t>
+          <t>S. CAMPBELL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.7005</v>
+        <v>2.6224</v>
       </c>
       <c r="E17" t="n">
-        <v>5.5375</v>
+        <v>4.7867</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.837</v>
+        <v>-2.1642</v>
       </c>
       <c r="G17" t="n">
-        <v>3.121</v>
+        <v>-1.2079</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8983</v>
+        <v>-0.6874</v>
       </c>
       <c r="I17" t="n">
-        <v>4.0192</v>
+        <v>-0.5205</v>
       </c>
       <c r="J17" t="n">
-        <v>6.9111</v>
+        <v>2.3088</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0918</v>
+        <v>1.1692</v>
       </c>
       <c r="L17" t="n">
-        <v>5.8193</v>
+        <v>1.1396</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.7902</v>
+        <v>-3.5167</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.9901</v>
+        <v>-1.8566</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.8001</v>
+        <v>-1.6601</v>
       </c>
       <c r="P17" t="n">
+        <v>1.3511</v>
+      </c>
+      <c r="Q17" t="n">
         <v>-0.965</v>
       </c>
-      <c r="Q17" t="n">
-        <v>-2.8951</v>
-      </c>
       <c r="R17" t="n">
-        <v>1.9301</v>
+        <v>2.3161</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4554</v>
+        <v>2.1512</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2935</v>
+        <v>1.6433</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7489</v>
+        <v>0.5079</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.3281</v>
       </c>
       <c r="W17" t="n">
-        <v>1.228</v>
+        <v>1.7997</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.228</v>
+        <v>-1.4716</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4073</v>
+        <v>1.3152</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4074</v>
+        <v>2.2085</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.0001</v>
+        <v>-0.8933</v>
       </c>
       <c r="G18" t="n">
         <v>1.7803</v>
@@ -1858,13 +1858,13 @@
         <v>1.5441</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2849</v>
+        <v>0.623</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7442</v>
+        <v>0.0569</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4594</v>
+        <v>0.5661</v>
       </c>
       <c r="V18" t="n">
         <v>1.228</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1864</v>
+        <v>0.4941</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8771</v>
+        <v>1.4779</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0635</v>
+        <v>-0.9839</v>
       </c>
       <c r="G19" t="n">
         <v>-1.2181</v>
@@ -1936,13 +1936,13 @@
         <v>1.9301</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.154</v>
+        <v>0.5265</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9373</v>
+        <v>-0.3364</v>
       </c>
       <c r="U19" t="n">
-        <v>0.7832</v>
+        <v>0.8629</v>
       </c>
       <c r="V19" t="n">
         <v>1.1857</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3173</v>
+        <v>-0.6497000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5790999999999999</v>
+        <v>-0.1785</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7383</v>
+        <v>-0.4712</v>
       </c>
       <c r="G20" t="n">
         <v>-1.4479</v>
@@ -2014,13 +2014,13 @@
         <v>0.965</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5486</v>
+        <v>0.119</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1785</v>
+        <v>0.2221</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3702</v>
+        <v>-0.1031</v>
       </c>
       <c r="V20" t="n">
         <v>-0.2859</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.9326</v>
+        <v>-2.4187</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.9986</v>
+        <v>-1.6982</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9340000000000001</v>
+        <v>-0.7205</v>
       </c>
       <c r="G21" t="n">
         <v>-2.4468</v>
@@ -2092,13 +2092,13 @@
         <v>0.579</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4508</v>
+        <v>0.0631</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7733</v>
+        <v>-0.4729</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3225</v>
+        <v>0.536</v>
       </c>
       <c r="V21" t="n">
         <v>-0.614</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.7458</v>
+        <v>-2.7222</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.4226</v>
+        <v>-0.1208</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.3232</v>
+        <v>-2.6014</v>
       </c>
       <c r="G22" t="n">
         <v>-4.927</v>
@@ -2170,13 +2170,13 @@
         <v>2.3161</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.9393</v>
+        <v>0.0843</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.3986</v>
+        <v>-0.0968</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5407</v>
+        <v>0.1811</v>
       </c>
       <c r="V22" t="n">
         <v>2.6996</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>3.655600000000002</v>
+        <v>6.325999999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>17.6166</v>
+        <v>17.6165</v>
       </c>
       <c r="F23" t="n">
-        <v>-13.961</v>
+        <v>-11.2905</v>
       </c>
       <c r="G23" t="n">
         <v>-3.247399999999999</v>
@@ -2239,7 +2239,7 @@
         <v>-7.6652</v>
       </c>
       <c r="P23" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>-1.110223024625157e-16</v>
       </c>
       <c r="Q23" t="n">
         <v>-12.5455</v>
@@ -2248,13 +2248,13 @@
         <v>12.5455</v>
       </c>
       <c r="S23" t="n">
-        <v>1.7054</v>
+        <v>4.3758</v>
       </c>
       <c r="T23" t="n">
-        <v>1.6858</v>
+        <v>1.6859</v>
       </c>
       <c r="U23" t="n">
-        <v>0.01950000000000007</v>
+        <v>2.69</v>
       </c>
       <c r="V23" t="n">
         <v>5.1977</v>
